--- a/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE405_Introduction to Deep Learning/SCORE_405.xlsx
+++ b/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE405_Introduction to Deep Learning/SCORE_405.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE405_Introduction to Deep Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4697579E-E874-4ED5-A276-F91B37988509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53083D99-D8E2-4AA9-9C3C-53DEE4246DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="2595" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -843,12 +843,16 @@
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2">
+        <v>17.600000000000001</v>
+      </c>
       <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+      <c r="M8" s="2">
+        <v>5</v>
+      </c>
       <c r="N8" s="2">
         <f>SUM(D8:M8)</f>
-        <v>44.18</v>
+        <v>66.78</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -878,12 +882,16 @@
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="2"/>
+      <c r="K9" s="2">
+        <v>6.8</v>
+      </c>
       <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="M9" s="2">
+        <v>5</v>
+      </c>
       <c r="N9" s="2">
         <f>SUM(D9:M9)</f>
-        <v>26.2</v>
+        <v>38</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -913,12 +921,16 @@
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="2"/>
+      <c r="K10" s="2">
+        <v>1.2</v>
+      </c>
       <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="M10" s="2">
+        <v>4</v>
+      </c>
       <c r="N10" s="2">
         <f>SUM(D10:M10)</f>
-        <v>24.54</v>
+        <v>29.74</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -948,12 +960,16 @@
       </c>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
+      <c r="K11" s="12">
+        <v>8</v>
+      </c>
       <c r="L11" s="12"/>
-      <c r="M11" s="2"/>
+      <c r="M11" s="2">
+        <v>5</v>
+      </c>
       <c r="N11" s="2">
         <f t="shared" ref="N11:N17" si="0">SUM(D11:M11)</f>
-        <v>22.3</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -983,12 +999,16 @@
       </c>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
+      <c r="K12" s="12">
+        <v>11.2</v>
+      </c>
       <c r="L12" s="12"/>
-      <c r="M12" s="2"/>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
       <c r="N12" s="2">
         <f t="shared" si="0"/>
-        <v>30.28</v>
+        <v>46.480000000000004</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -1018,12 +1038,16 @@
       </c>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
+      <c r="K13" s="12">
+        <v>10.4</v>
+      </c>
       <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
+      <c r="M13" s="12">
+        <v>5</v>
+      </c>
       <c r="N13" s="2">
         <f t="shared" si="0"/>
-        <v>35.54</v>
+        <v>50.94</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -1053,12 +1077,16 @@
       </c>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
+      <c r="K14" s="12">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
+      <c r="M14" s="12">
+        <v>4</v>
+      </c>
       <c r="N14" s="2">
         <f t="shared" si="0"/>
-        <v>27.7</v>
+        <v>40.5</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -1088,12 +1116,16 @@
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
+      <c r="K15" s="12">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
+      <c r="M15" s="12">
+        <v>5</v>
+      </c>
       <c r="N15" s="2">
         <f t="shared" si="0"/>
-        <v>28.64</v>
+        <v>42.84</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -1123,12 +1155,16 @@
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
+      <c r="K16" s="12">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
+      <c r="M16" s="12">
+        <v>5</v>
+      </c>
       <c r="N16" s="2">
         <f t="shared" si="0"/>
-        <v>22.8</v>
+        <v>37</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -1158,12 +1194,16 @@
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
+      <c r="K17" s="12">
+        <v>12.4</v>
+      </c>
       <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
+      <c r="M17" s="12">
+        <v>5</v>
+      </c>
       <c r="N17" s="2">
         <f t="shared" si="0"/>
-        <v>17.14</v>
+        <v>34.54</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -1176,7 +1216,7 @@
       </c>
       <c r="N18" s="6">
         <f>AVERAGE(N8:N17)</f>
-        <v>27.931999999999999</v>
+        <v>42.212000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -1185,7 +1225,7 @@
       </c>
       <c r="N19" s="2">
         <f>_xlfn.STDEV.P(N8:N17)</f>
-        <v>7.1901109866260056</v>
+        <v>10.04190101524606</v>
       </c>
     </row>
   </sheetData>

--- a/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE405_Introduction to Deep Learning/SCORE_405.xlsx
+++ b/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE405_Introduction to Deep Learning/SCORE_405.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE405_Introduction to Deep Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53083D99-D8E2-4AA9-9C3C-53DEE4246DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94820A75-5F06-46EF-A32E-813FACDB7B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="2595" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5805" yWindow="2940" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ประวัติการศึกษา" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>มหาวิทยาลัยเทคโนโลยีราชมงคลล้านนา เชียงราย</t>
   </si>
@@ -201,7 +201,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -219,19 +219,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -269,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -281,23 +268,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -609,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="24" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -633,157 +613,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14" t="s">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14" t="s">
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="14" t="s">
+      <c r="O5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="14" t="s">
+      <c r="P5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="Q5" s="14" t="s">
+      <c r="Q5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="R5" s="14" t="s">
+      <c r="R5" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
       <c r="D7" s="4" t="s">
         <v>35</v>
       </c>
@@ -814,20 +794,20 @@
       <c r="M7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7">
+      <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="3"/>
@@ -846,27 +826,41 @@
       <c r="K8" s="2">
         <v>17.600000000000001</v>
       </c>
-      <c r="L8" s="2"/>
+      <c r="L8" s="2">
+        <v>24</v>
+      </c>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
         <f>SUM(D8:M8)</f>
-        <v>66.78</v>
-      </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="4"/>
+        <v>90.78</v>
+      </c>
+      <c r="O8" s="2">
+        <f>AVERAGE($N$8:$N$17)</f>
+        <v>58.482000000000006</v>
+      </c>
+      <c r="P8" s="2">
+        <f>_xlfn.STDEV.S($N$8:$N$17)</f>
+        <v>12.659971739480431</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>(N8 - $O$8) / $P$8</f>
+        <v>2.5511905290655501</v>
+      </c>
+      <c r="R8" s="4" t="str">
+        <f>IF(N8&lt;45, "F", IF((Q8*10)+50&gt;=65, "A", IF((Q8*10)+50&gt;=60, "B+", IF((Q8*10)+50&gt;=55, "B", IF((Q8*10)+50&gt;=50, "C+", IF((Q8*10)+50&gt;=45, "C", IF((Q8*10)+50&gt;=40, "D+", IF((Q8*10)+50&gt;=35, "D", "F"))))))))</f>
+        <v>A</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="7">
+      <c r="A9" s="5">
         <v>2</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="3"/>
@@ -885,31 +879,45 @@
       <c r="K9" s="2">
         <v>6.8</v>
       </c>
-      <c r="L9" s="2"/>
+      <c r="L9" s="2">
+        <v>15.5</v>
+      </c>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
         <f>SUM(D9:M9)</f>
-        <v>38</v>
-      </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="4"/>
+        <v>53.5</v>
+      </c>
+      <c r="O9" s="2">
+        <f t="shared" ref="O9:O17" si="0">AVERAGE($N$8:$N$17)</f>
+        <v>58.482000000000006</v>
+      </c>
+      <c r="P9" s="2">
+        <f t="shared" ref="P9:P17" si="1">_xlfn.STDEV.S($N$8:$N$17)</f>
+        <v>12.659971739480431</v>
+      </c>
+      <c r="Q9" s="2">
+        <f t="shared" ref="Q9:Q17" si="2">(N9 - $O$8) / $P$8</f>
+        <v>-0.39352378524381043</v>
+      </c>
+      <c r="R9" s="9" t="str">
+        <f>IF(N9&lt;45, "F", IF((Q9*10)+50&gt;=65, "A", IF((Q9*10)+50&gt;=60, "B+", IF((Q9*10)+50&gt;=55, "B", IF((Q9*10)+50&gt;=50, "C+", IF((Q9*10)+50&gt;=45, "C", IF((Q9*10)+50&gt;=40, "D+", IF((Q9*10)+50&gt;=35, "D", "F"))))))))</f>
+        <v>C</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7">
+      <c r="A10" s="5">
         <v>3</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="8"/>
+      <c r="E10" s="6"/>
       <c r="F10" s="2">
         <v>7.54</v>
       </c>
@@ -924,308 +932,402 @@
       <c r="K10" s="2">
         <v>1.2</v>
       </c>
-      <c r="L10" s="2"/>
+      <c r="L10" s="2">
+        <v>23</v>
+      </c>
       <c r="M10" s="2">
         <v>4</v>
       </c>
       <c r="N10" s="2">
         <f>SUM(D10:M10)</f>
-        <v>29.74</v>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="4"/>
+        <v>52.739999999999995</v>
+      </c>
+      <c r="O10" s="2">
+        <f>AVERAGE($N$8:$N$17)</f>
+        <v>58.482000000000006</v>
+      </c>
+      <c r="P10" s="2">
+        <f t="shared" si="1"/>
+        <v>12.659971739480431</v>
+      </c>
+      <c r="Q10" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.45355551482737078</v>
+      </c>
+      <c r="R10" s="9" t="str">
+        <f t="shared" ref="R9:R17" si="3">IF(N10&lt;45, "F", IF((Q10*10)+50&gt;=65, "A", IF((Q10*10)+50&gt;=60, "B+", IF((Q10*10)+50&gt;=55, "B", IF((Q10*10)+50&gt;=50, "C+", IF((Q10*10)+50&gt;=45, "C", IF((Q10*10)+50&gt;=40, "D+", IF((Q10*10)+50&gt;=35, "D", "F"))))))))</f>
+        <v>C</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="7">
+      <c r="A11" s="5">
         <v>4</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8">
         <v>6.8</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="8">
         <v>10.5</v>
       </c>
-      <c r="H11" s="12">
-        <v>5</v>
-      </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12">
+      <c r="H11" s="8">
+        <v>5</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8">
         <v>8</v>
       </c>
-      <c r="L11" s="12"/>
+      <c r="L11" s="8">
+        <v>13.5</v>
+      </c>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <f t="shared" ref="N11:N17" si="0">SUM(D11:M11)</f>
-        <v>35.299999999999997</v>
-      </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
+        <f t="shared" ref="N11:N17" si="4">SUM(D11:M11)</f>
+        <v>48.8</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" si="0"/>
+        <v>58.482000000000006</v>
+      </c>
+      <c r="P11" s="2">
+        <f t="shared" si="1"/>
+        <v>12.659971739480431</v>
+      </c>
+      <c r="Q11" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.76477263924740491</v>
+      </c>
+      <c r="R11" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>D+</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7">
-        <v>5</v>
-      </c>
-      <c r="B12" s="7" t="s">
+      <c r="A12" s="5">
+        <v>5</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8">
         <v>6.08</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="8">
         <v>19.2</v>
       </c>
-      <c r="H12" s="12">
-        <v>5</v>
-      </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12">
+      <c r="H12" s="8">
+        <v>5</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8">
         <v>11.2</v>
       </c>
-      <c r="L12" s="12"/>
+      <c r="L12" s="8">
+        <v>15.5</v>
+      </c>
       <c r="M12" s="2">
         <v>5</v>
       </c>
       <c r="N12" s="2">
+        <f t="shared" si="4"/>
+        <v>61.980000000000004</v>
+      </c>
+      <c r="O12" s="2">
         <f t="shared" si="0"/>
-        <v>46.480000000000004</v>
-      </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
+        <v>58.482000000000006</v>
+      </c>
+      <c r="P12" s="2">
+        <f t="shared" si="1"/>
+        <v>12.659971739480431</v>
+      </c>
+      <c r="Q12" s="2">
+        <f t="shared" si="2"/>
+        <v>0.27630393432012168</v>
+      </c>
+      <c r="R12" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>C+</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7">
+      <c r="A13" s="5">
         <v>6</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8">
         <v>8.34</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="8">
         <v>22.2</v>
       </c>
-      <c r="H13" s="12">
-        <v>5</v>
-      </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12">
+      <c r="H13" s="8">
+        <v>5</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8">
         <v>10.4</v>
       </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12">
+      <c r="L13" s="8">
+        <v>14</v>
+      </c>
+      <c r="M13" s="8">
         <v>5</v>
       </c>
       <c r="N13" s="2">
+        <f t="shared" si="4"/>
+        <v>64.94</v>
+      </c>
+      <c r="O13" s="2">
         <f t="shared" si="0"/>
-        <v>50.94</v>
-      </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
+        <v>58.482000000000006</v>
+      </c>
+      <c r="P13" s="2">
+        <f t="shared" si="1"/>
+        <v>12.659971739480431</v>
+      </c>
+      <c r="Q13" s="2">
+        <f t="shared" si="2"/>
+        <v>0.51011172322451248</v>
+      </c>
+      <c r="R13" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>B</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7">
+      <c r="A14" s="5">
         <v>7</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8">
         <v>7</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="8">
         <v>15.7</v>
       </c>
-      <c r="H14" s="12">
-        <v>5</v>
-      </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12">
+      <c r="H14" s="8">
+        <v>5</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8">
         <v>8.8000000000000007</v>
       </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12">
+      <c r="L14" s="8">
+        <v>16</v>
+      </c>
+      <c r="M14" s="8">
         <v>4</v>
       </c>
       <c r="N14" s="2">
+        <f t="shared" si="4"/>
+        <v>56.5</v>
+      </c>
+      <c r="O14" s="2">
         <f t="shared" si="0"/>
-        <v>40.5</v>
-      </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
+        <v>58.482000000000006</v>
+      </c>
+      <c r="P14" s="2">
+        <f t="shared" si="1"/>
+        <v>12.659971739480431</v>
+      </c>
+      <c r="Q14" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.15655643162449495</v>
+      </c>
+      <c r="R14" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="7">
+      <c r="A15" s="5">
         <v>8</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8">
         <v>6.14</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="8">
         <v>18</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="8">
         <v>4.5</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12">
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8">
         <v>9.1999999999999993</v>
       </c>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12">
+      <c r="L15" s="8">
+        <v>14.5</v>
+      </c>
+      <c r="M15" s="8">
         <v>5</v>
       </c>
       <c r="N15" s="2">
+        <f t="shared" si="4"/>
+        <v>57.34</v>
+      </c>
+      <c r="O15" s="2">
         <f t="shared" si="0"/>
-        <v>42.84</v>
-      </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
+        <v>58.482000000000006</v>
+      </c>
+      <c r="P15" s="2">
+        <f t="shared" si="1"/>
+        <v>12.659971739480431</v>
+      </c>
+      <c r="Q15" s="2">
+        <f t="shared" si="2"/>
+        <v>-9.0205572611086332E-2</v>
+      </c>
+      <c r="R15" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="7">
+      <c r="A16" s="5">
         <v>9</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12">
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8">
         <v>3.8</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="8">
         <v>14</v>
       </c>
-      <c r="H16" s="12">
-        <v>5</v>
-      </c>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12">
+      <c r="H16" s="8">
+        <v>5</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8">
         <v>9.1999999999999993</v>
       </c>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12">
+      <c r="L16" s="8">
+        <v>14.7</v>
+      </c>
+      <c r="M16" s="8">
         <v>5</v>
       </c>
       <c r="N16" s="2">
+        <f t="shared" si="4"/>
+        <v>51.7</v>
+      </c>
+      <c r="O16" s="2">
         <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
+        <v>58.482000000000006</v>
+      </c>
+      <c r="P16" s="2">
+        <f t="shared" si="1"/>
+        <v>12.659971739480431</v>
+      </c>
+      <c r="Q16" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.53570419741539954</v>
+      </c>
+      <c r="R16" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>D+</v>
+      </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="7">
+      <c r="A17" s="5">
         <v>10</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12">
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8">
         <v>8.14</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="8">
         <v>5.5</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="8">
         <v>3.5</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12">
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8">
         <v>12.4</v>
       </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12">
+      <c r="L17" s="8">
+        <v>12</v>
+      </c>
+      <c r="M17" s="8">
         <v>5</v>
       </c>
       <c r="N17" s="2">
+        <f t="shared" si="4"/>
+        <v>46.54</v>
+      </c>
+      <c r="O17" s="2">
         <f t="shared" si="0"/>
-        <v>34.54</v>
-      </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="M18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="N18" s="6">
-        <f>AVERAGE(N8:N17)</f>
-        <v>42.212000000000003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="M19" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="N19" s="2">
-        <f>_xlfn.STDEV.P(N8:N17)</f>
-        <v>10.04190101524606</v>
+        <v>58.482000000000006</v>
+      </c>
+      <c r="P17" s="2">
+        <f t="shared" si="1"/>
+        <v>12.659971739480431</v>
+      </c>
+      <c r="Q17" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.94328804564062241</v>
+      </c>
+      <c r="R17" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>D+</v>
       </c>
     </row>
   </sheetData>

--- a/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE405_Introduction to Deep Learning/SCORE_405.xlsx
+++ b/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE405_Introduction to Deep Learning/SCORE_405.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE405_Introduction to Deep Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94820A75-5F06-46EF-A32E-813FACDB7B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01D66E2-150F-43B6-9C22-FFB71329AA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5805" yWindow="2940" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -955,7 +955,7 @@
         <v>-0.45355551482737078</v>
       </c>
       <c r="R10" s="9" t="str">
-        <f t="shared" ref="R9:R17" si="3">IF(N10&lt;45, "F", IF((Q10*10)+50&gt;=65, "A", IF((Q10*10)+50&gt;=60, "B+", IF((Q10*10)+50&gt;=55, "B", IF((Q10*10)+50&gt;=50, "C+", IF((Q10*10)+50&gt;=45, "C", IF((Q10*10)+50&gt;=40, "D+", IF((Q10*10)+50&gt;=35, "D", "F"))))))))</f>
+        <f t="shared" ref="R10:R17" si="3">IF(N10&lt;45, "F", IF((Q10*10)+50&gt;=65, "A", IF((Q10*10)+50&gt;=60, "B+", IF((Q10*10)+50&gt;=55, "B", IF((Q10*10)+50&gt;=50, "C+", IF((Q10*10)+50&gt;=45, "C", IF((Q10*10)+50&gt;=40, "D+", IF((Q10*10)+50&gt;=35, "D", "F"))))))))</f>
         <v>C</v>
       </c>
     </row>
